--- a/erp-server/erp-server-tms/src/main/resources/excel/declareExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/declareExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
   <si>
     <t>中华人民共和国海关出口货物报关单</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>境内发货人</t>
-  </si>
-  <si>
-    <t>91440300MA5DN1AA1R（4403161PVZ）</t>
   </si>
   <si>
     <t>出境关别</t>
@@ -1542,9 +1539,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1976,16 +1970,14 @@
         <v>5</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="119" t="s">
-        <v>6</v>
-      </c>
+      <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
@@ -1993,12 +1985,12 @@
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
       <c r="M3" s="15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
       <c r="P3" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q3" s="15"/>
       <c r="R3" s="15"/>
@@ -2006,17 +1998,17 @@
     </row>
     <row r="4" ht="14.25" spans="1:19">
       <c r="A4" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="18"/>
       <c r="D4" s="16"/>
       <c r="E4" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
@@ -2024,7 +2016,7 @@
       <c r="K4" s="19"/>
       <c r="L4" s="19"/>
       <c r="M4" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N4" s="19"/>
       <c r="O4" s="19"/>
@@ -2035,17 +2027,17 @@
     </row>
     <row r="5" ht="14.25" spans="1:19">
       <c r="A5" s="20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="22"/>
       <c r="D5" s="20"/>
       <c r="E5" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -2053,7 +2045,7 @@
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N5" s="78"/>
       <c r="O5" s="14"/>
@@ -2064,13 +2056,13 @@
     </row>
     <row r="6" ht="14.25" spans="1:19">
       <c r="A6" s="23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="25"/>
       <c r="D6" s="23"/>
       <c r="E6" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="19"/>
@@ -2080,7 +2072,7 @@
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
       <c r="M6" s="79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N6" s="80"/>
       <c r="O6" s="81"/>
@@ -2091,19 +2083,17 @@
     </row>
     <row r="7" ht="14.25" spans="1:19">
       <c r="A7" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="27"/>
-      <c r="C7" s="119" t="s">
-        <v>6</v>
-      </c>
+      <c r="C7" s="12"/>
       <c r="D7" s="12"/>
       <c r="E7" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
@@ -2111,7 +2101,7 @@
       <c r="K7" s="82"/>
       <c r="L7" s="82"/>
       <c r="M7" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N7" s="78"/>
       <c r="O7" s="14"/>
@@ -2122,17 +2112,17 @@
     </row>
     <row r="8" ht="14.25" spans="1:19">
       <c r="A8" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="18"/>
       <c r="D8" s="16"/>
       <c r="E8" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
@@ -2140,7 +2130,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N8" s="85"/>
       <c r="O8" s="86"/>
@@ -2151,27 +2141,27 @@
     </row>
     <row r="9" ht="14.25" spans="1:19">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="29"/>
       <c r="D9" s="14"/>
       <c r="E9" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="J9" s="87"/>
       <c r="K9" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L9" s="14"/>
       <c r="M9" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" s="78"/>
       <c r="O9" s="78"/>
@@ -2182,27 +2172,27 @@
     </row>
     <row r="10" ht="14.25" spans="1:19">
       <c r="A10" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="32"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="19"/>
       <c r="I10" s="19"/>
       <c r="J10" s="34"/>
       <c r="K10" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N10" s="19"/>
       <c r="O10" s="19"/>
@@ -2213,81 +2203,81 @@
     </row>
     <row r="11" ht="14.25" spans="1:19">
       <c r="A11" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="29"/>
       <c r="D11" s="14"/>
       <c r="E11" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="G11" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>42</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
       <c r="J11" s="77"/>
       <c r="K11" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L11" s="14"/>
       <c r="M11" s="88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N11" s="88"/>
       <c r="O11" s="88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P11" s="88"/>
       <c r="Q11" s="88"/>
       <c r="R11" s="88" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S11" s="88"/>
     </row>
     <row r="12" ht="14.25" spans="1:19">
       <c r="A12" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="32"/>
       <c r="D12" s="16"/>
       <c r="E12" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="G12" s="34" t="s">
         <v>49</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>50</v>
       </c>
       <c r="H12" s="34"/>
       <c r="I12" s="34"/>
       <c r="J12" s="34"/>
       <c r="K12" s="79" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L12" s="81"/>
       <c r="M12" s="89" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N12" s="19"/>
       <c r="O12" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P12" s="19"/>
       <c r="Q12" s="19"/>
       <c r="R12" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S12" s="19"/>
     </row>
     <row r="13" ht="14.25" spans="1:19">
       <c r="A13" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="35"/>
@@ -2310,7 +2300,7 @@
     </row>
     <row r="14" ht="14.25" spans="1:19">
       <c r="A14" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="38"/>
       <c r="C14" s="39"/>
@@ -2333,14 +2323,14 @@
     </row>
     <row r="15" ht="14.25" spans="1:19">
       <c r="A15" s="42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="43"/>
       <c r="C15" s="44"/>
       <c r="D15" s="45"/>
       <c r="E15" s="45"/>
       <c r="F15" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15" s="47"/>
       <c r="H15" s="47"/>
@@ -2358,7 +2348,7 @@
     </row>
     <row r="16" ht="14.25" spans="1:19">
       <c r="A16" s="37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="38"/>
       <c r="C16" s="39"/>
@@ -2381,44 +2371,44 @@
     </row>
     <row r="17" ht="42.75" spans="1:19">
       <c r="A17" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="C17" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="D17" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="E17" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="48" t="s">
+      <c r="F17" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="G17" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="H17" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="I17" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="I17" s="48" t="s">
+      <c r="J17" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="48" t="s">
+      <c r="K17" s="48" t="s">
         <v>69</v>
-      </c>
-      <c r="K17" s="48" t="s">
-        <v>70</v>
       </c>
       <c r="L17" s="48"/>
       <c r="M17" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="N17" s="48" t="s">
         <v>71</v>
-      </c>
-      <c r="N17" s="48" t="s">
-        <v>72</v>
       </c>
       <c r="O17" s="48"/>
       <c r="P17" s="48"/>
@@ -2428,44 +2418,44 @@
     </row>
     <row r="18" ht="28.5" spans="1:19">
       <c r="A18" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="C18" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="D18" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="E18" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="F18" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="57" t="s">
+      <c r="G18" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="H18" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="H18" s="59" t="s">
+      <c r="I18" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="94" t="s">
+      <c r="J18" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="J18" s="94" t="s">
+      <c r="K18" s="95" t="s">
         <v>82</v>
-      </c>
-      <c r="K18" s="95" t="s">
-        <v>83</v>
       </c>
       <c r="L18" s="96"/>
       <c r="M18" s="97" t="s">
+        <v>83</v>
+      </c>
+      <c r="N18" s="97" t="s">
         <v>84</v>
-      </c>
-      <c r="N18" s="97" t="s">
-        <v>85</v>
       </c>
       <c r="O18" s="97"/>
       <c r="P18" s="97"/>
@@ -2475,7 +2465,7 @@
     </row>
     <row r="19" ht="14.25" spans="1:19">
       <c r="A19" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="60"/>
@@ -2483,10 +2473,10 @@
       <c r="E19" s="31"/>
       <c r="F19" s="31"/>
       <c r="G19" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="61" t="s">
         <v>87</v>
-      </c>
-      <c r="H19" s="61" t="s">
-        <v>88</v>
       </c>
       <c r="I19" s="62"/>
       <c r="J19" s="98"/>
@@ -2505,41 +2495,41 @@
       <c r="B20" s="28"/>
       <c r="C20" s="60"/>
       <c r="D20" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="31" t="s">
         <v>89</v>
-      </c>
-      <c r="E20" s="31" t="s">
-        <v>90</v>
       </c>
       <c r="F20" s="31"/>
       <c r="G20" s="62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H20" s="62"/>
       <c r="I20" s="62"/>
       <c r="J20" s="98" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K20" s="62"/>
       <c r="L20" s="62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M20" s="62"/>
       <c r="N20" s="62"/>
       <c r="O20" s="62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P20" s="62"/>
       <c r="Q20" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R20" s="62"/>
       <c r="S20" s="61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:19">
       <c r="A21" s="42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21" s="43"/>
       <c r="C21" s="44"/>
@@ -2547,7 +2537,7 @@
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
       <c r="G21" s="47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H21" s="47"/>
       <c r="I21" s="47"/>
@@ -2557,7 +2547,7 @@
       <c r="M21" s="47"/>
       <c r="N21" s="102"/>
       <c r="O21" s="103" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P21" s="47"/>
       <c r="Q21" s="47"/>
@@ -2587,7 +2577,7 @@
     </row>
     <row r="23" ht="14.25" spans="1:19">
       <c r="A23" s="68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23" s="69"/>
       <c r="C23" s="70"/>
@@ -2600,7 +2590,7 @@
       <c r="J23" s="107"/>
       <c r="K23" s="72"/>
       <c r="L23" s="72" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M23" s="72"/>
       <c r="N23" s="72"/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/declareExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/declareExport.xlsx
@@ -7,29 +7,15 @@
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="报关单" sheetId="1" r:id="rId1"/>
+    <sheet name="合同" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="161">
   <si>
     <t>中华人民共和国海关出口货物报关单</t>
   </si>
@@ -342,6 +328,203 @@
   </si>
   <si>
     <t>申报单位(签章)</t>
+  </si>
+  <si>
+    <t>合    同</t>
+  </si>
+  <si>
+    <t>卖 方</t>
+  </si>
+  <si>
+    <t>{sellerName}</t>
+  </si>
+  <si>
+    <t>合同号码</t>
+  </si>
+  <si>
+    <t>{contractNo}</t>
+  </si>
+  <si>
+    <t>Sellers:</t>
+  </si>
+  <si>
+    <t>Contract No:</t>
+  </si>
+  <si>
+    <t>地 址</t>
+  </si>
+  <si>
+    <t>{sellerAddress}</t>
+  </si>
+  <si>
+    <t>日 期</t>
+  </si>
+  <si>
+    <t>{contractDate}</t>
+  </si>
+  <si>
+    <t>Address:</t>
+  </si>
+  <si>
+    <t>Date:</t>
+  </si>
+  <si>
+    <t>电 话</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>签约地点</t>
+  </si>
+  <si>
+    <t>深圳</t>
+  </si>
+  <si>
+    <t>TEL:</t>
+  </si>
+  <si>
+    <t>Signed at:</t>
+  </si>
+  <si>
+    <t>买 方</t>
+  </si>
+  <si>
+    <t>{buyerName}</t>
+  </si>
+  <si>
+    <t>Buyers:</t>
+  </si>
+  <si>
+    <t>地 址</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Address:</t>
+  </si>
+  <si>
+    <t>电 话</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>TEL:</t>
+  </si>
+  <si>
+    <t>经买卖双方确认根据下列条款订立本合同</t>
+  </si>
+  <si>
+    <t>This contract is made out by the Sellers and Buyers as per the following terms and conditions mutually confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1)货物名称及规格
+Name of commodity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2)数量
+Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3)单位
+Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4)单价
+Unit Price</t>
+  </si>
+  <si>
+    <t>币种</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5)金额
+Amount</t>
+  </si>
+  <si>
+    <t>{contractDetail.declareChineseName}</t>
+  </si>
+  <si>
+    <t>{contractDetail.qty}</t>
+  </si>
+  <si>
+    <t>{contractDetail.declareUnitName}</t>
+  </si>
+  <si>
+    <t>{contractDetail.price}</t>
+  </si>
+  <si>
+    <t>{contractDetail.declareCurrency}</t>
+  </si>
+  <si>
+    <t>{contractDetail.totalPrice}</t>
+  </si>
+  <si>
+    <t>数量及总价允许有 2% 的增减。</t>
+  </si>
+  <si>
+    <t>2% more or less both in amount and quantity allowed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">总 值
+Total Amount:</t>
+  </si>
+  <si>
+    <t>{currency} {totalAmount}</t>
+  </si>
+  <si>
+    <t>合同总值（大写）</t>
+  </si>
+  <si>
+    <t>{totalAmountUpper}</t>
+  </si>
+  <si>
+    <t>Total Value in Word:</t>
+  </si>
+  <si>
+    <t>包装及唛头</t>
+  </si>
+  <si>
+    <t>{packingMarks}</t>
+  </si>
+  <si>
+    <t>Packing and Shipping Marks:</t>
+  </si>
+  <si>
+    <t>装运日期</t>
+  </si>
+  <si>
+    <t>三个月之前</t>
+  </si>
+  <si>
+    <t>Time of Shipment:</t>
+  </si>
+  <si>
+    <t>装运口岸和目的地</t>
+  </si>
+  <si>
+    <t>深圳 to {destination}</t>
+  </si>
+  <si>
+    <t>Loading Port &amp; Destination:</t>
+  </si>
+  <si>
+    <t>付款条件</t>
+  </si>
+  <si>
+    <t>{paymentTerms}</t>
+  </si>
+  <si>
+    <t>Terms of Payment:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卖 方
+THE SELLERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">买 方
+THE BUYERS</t>
   </si>
 </sst>
 </file>
@@ -2692,25 +2875,298 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" t="s" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="F4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="F20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B28" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B30" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="B4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B8:F9"/>
+    <mergeCell ref="B10:F11"/>
+    <mergeCell ref="B12:F13"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:F29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:F31"/>
+    <mergeCell ref="A33:C35"/>
+    <mergeCell ref="D33:F35"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/declareExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/declareExport.xlsx
@@ -1,21 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
-    <sheet name="合同" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
   <si>
     <t>中华人民共和国海关出口货物报关单</t>
   </si>
@@ -329,203 +341,6 @@
   <si>
     <t>申报单位(签章)</t>
   </si>
-  <si>
-    <t>合    同</t>
-  </si>
-  <si>
-    <t>卖 方</t>
-  </si>
-  <si>
-    <t>{sellerName}</t>
-  </si>
-  <si>
-    <t>合同号码</t>
-  </si>
-  <si>
-    <t>{contractNo}</t>
-  </si>
-  <si>
-    <t>Sellers:</t>
-  </si>
-  <si>
-    <t>Contract No:</t>
-  </si>
-  <si>
-    <t>地 址</t>
-  </si>
-  <si>
-    <t>{sellerAddress}</t>
-  </si>
-  <si>
-    <t>日 期</t>
-  </si>
-  <si>
-    <t>{contractDate}</t>
-  </si>
-  <si>
-    <t>Address:</t>
-  </si>
-  <si>
-    <t>Date:</t>
-  </si>
-  <si>
-    <t>电 话</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>签约地点</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>TEL:</t>
-  </si>
-  <si>
-    <t>Signed at:</t>
-  </si>
-  <si>
-    <t>买 方</t>
-  </si>
-  <si>
-    <t>{buyerName}</t>
-  </si>
-  <si>
-    <t>Buyers:</t>
-  </si>
-  <si>
-    <t>地 址</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Address:</t>
-  </si>
-  <si>
-    <t>电 话</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>TEL:</t>
-  </si>
-  <si>
-    <t>经买卖双方确认根据下列条款订立本合同</t>
-  </si>
-  <si>
-    <t>This contract is made out by the Sellers and Buyers as per the following terms and conditions mutually confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1)货物名称及规格
-Name of commodity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2)数量
-Quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)单位
-Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4)单价
-Unit Price</t>
-  </si>
-  <si>
-    <t>币种</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5)金额
-Amount</t>
-  </si>
-  <si>
-    <t>{contractDetail.declareChineseName}</t>
-  </si>
-  <si>
-    <t>{contractDetail.qty}</t>
-  </si>
-  <si>
-    <t>{contractDetail.declareUnitName}</t>
-  </si>
-  <si>
-    <t>{contractDetail.price}</t>
-  </si>
-  <si>
-    <t>{contractDetail.declareCurrency}</t>
-  </si>
-  <si>
-    <t>{contractDetail.totalPrice}</t>
-  </si>
-  <si>
-    <t>数量及总价允许有 2% 的增减。</t>
-  </si>
-  <si>
-    <t>2% more or less both in amount and quantity allowed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">总 值
-Total Amount:</t>
-  </si>
-  <si>
-    <t>{currency} {totalAmount}</t>
-  </si>
-  <si>
-    <t>合同总值（大写）</t>
-  </si>
-  <si>
-    <t>{totalAmountUpper}</t>
-  </si>
-  <si>
-    <t>Total Value in Word:</t>
-  </si>
-  <si>
-    <t>包装及唛头</t>
-  </si>
-  <si>
-    <t>{packingMarks}</t>
-  </si>
-  <si>
-    <t>Packing and Shipping Marks:</t>
-  </si>
-  <si>
-    <t>装运日期</t>
-  </si>
-  <si>
-    <t>三个月之前</t>
-  </si>
-  <si>
-    <t>Time of Shipment:</t>
-  </si>
-  <si>
-    <t>装运口岸和目的地</t>
-  </si>
-  <si>
-    <t>深圳 to {destination}</t>
-  </si>
-  <si>
-    <t>Loading Port &amp; Destination:</t>
-  </si>
-  <si>
-    <t>付款条件</t>
-  </si>
-  <si>
-    <t>{paymentTerms}</t>
-  </si>
-  <si>
-    <t>Terms of Payment:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卖 方
-THE SELLERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">买 方
-THE BUYERS</t>
-  </si>
 </sst>
 </file>
 
@@ -538,8 +353,8 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="180" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
     <numFmt numFmtId="181" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
@@ -1024,7 +839,53 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -1052,9 +913,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1071,50 +930,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1381,6 +1196,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1396,6 +1214,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1414,62 +1241,122 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1477,7 +1364,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1492,22 +1382,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1519,13 +1427,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1543,19 +1451,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1570,7 +1502,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1585,142 +1526,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2108,7 +1923,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
-      <c r="J1" s="73"/>
+      <c r="J1" s="5"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -2120,667 +1935,667 @@
       <c r="S1" s="4"/>
     </row>
     <row r="2" ht="14.25" spans="1:19">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="76" t="s">
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="S2" s="76"/>
+      <c r="S2" s="13"/>
     </row>
     <row r="3" ht="14.25" spans="1:19">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="18"/>
+      <c r="G3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15" t="s">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15" t="s">
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
     </row>
     <row r="4" ht="14.25" spans="1:19">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="19" t="s">
+      <c r="F4" s="21"/>
+      <c r="G4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19" t="s">
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
     </row>
     <row r="5" ht="14.25" spans="1:19">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="13" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="13" t="s">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="78"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
     </row>
     <row r="6" ht="14.25" spans="1:19">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="16" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="79" t="s">
+      <c r="F6" s="21"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="80"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
     </row>
     <row r="7" ht="14.25" spans="1:19">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13" t="s">
+      <c r="B7" s="37"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15" t="s">
+      <c r="F7" s="18"/>
+      <c r="G7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="13" t="s">
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N7" s="78"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="61"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="41"/>
     </row>
     <row r="8" ht="14.25" spans="1:19">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="19" t="s">
+      <c r="F8" s="21"/>
+      <c r="G8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="84" t="s">
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="N8" s="85"/>
-      <c r="O8" s="86"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="45"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
     </row>
     <row r="9" ht="14.25" spans="1:19">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="10" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="30" t="s">
+      <c r="F9" s="14"/>
+      <c r="G9" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="13" t="s">
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="14"/>
-      <c r="M9" s="13" t="s">
+      <c r="L9" s="18"/>
+      <c r="M9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="78"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="112"/>
-      <c r="S9" s="113"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="53"/>
     </row>
     <row r="10" ht="14.25" spans="1:19">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="19" t="s">
+      <c r="F10" s="21"/>
+      <c r="G10" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="16" t="s">
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="19" t="s">
+      <c r="L10" s="21"/>
+      <c r="M10" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="114"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
     </row>
     <row r="11" ht="14.25" spans="1:19">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="13" t="s">
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="14"/>
-      <c r="M11" s="88" t="s">
+      <c r="L11" s="18"/>
+      <c r="M11" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="N11" s="88"/>
-      <c r="O11" s="88" t="s">
+      <c r="N11" s="56"/>
+      <c r="O11" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88" t="s">
+      <c r="P11" s="56"/>
+      <c r="Q11" s="56"/>
+      <c r="R11" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="S11" s="88"/>
+      <c r="S11" s="56"/>
     </row>
     <row r="12" ht="14.25" spans="1:19">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="19" t="s">
+      <c r="B12" s="22"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="F12" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="79" t="s">
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="81"/>
-      <c r="M12" s="89" t="s">
+      <c r="L12" s="35"/>
+      <c r="M12" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19" t="s">
+      <c r="N12" s="24"/>
+      <c r="O12" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19" t="s">
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="S12" s="19"/>
+      <c r="S12" s="24"/>
     </row>
     <row r="13" ht="14.25" spans="1:19">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="90"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="60"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
     </row>
     <row r="14" ht="14.25" spans="1:19">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="115"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="68"/>
     </row>
     <row r="15" ht="14.25" spans="1:19">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="46" t="s">
+      <c r="B15" s="70"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="102"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="76"/>
     </row>
     <row r="16" ht="14.25" spans="1:19">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="91"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="93"/>
-      <c r="P16" s="93"/>
-      <c r="Q16" s="93"/>
-      <c r="R16" s="93"/>
-      <c r="S16" s="116"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="66"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="77"/>
+      <c r="S16" s="78"/>
     </row>
     <row r="17" ht="42.75" spans="1:19">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="48" t="s">
+      <c r="E17" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="G17" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="H17" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="I17" s="48" t="s">
+      <c r="I17" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="J17" s="48" t="s">
+      <c r="J17" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="48" t="s">
+      <c r="K17" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48" t="s">
+      <c r="L17" s="79"/>
+      <c r="M17" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="N17" s="48" t="s">
+      <c r="N17" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="O17" s="48"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="48"/>
-      <c r="S17" s="48"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="79"/>
+      <c r="Q17" s="79"/>
+      <c r="R17" s="79"/>
+      <c r="S17" s="79"/>
     </row>
     <row r="18" ht="28.5" spans="1:19">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="57" t="s">
+      <c r="F18" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="G18" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="H18" s="59" t="s">
+      <c r="H18" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="I18" s="94" t="s">
+      <c r="I18" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="J18" s="94" t="s">
+      <c r="J18" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="K18" s="95" t="s">
+      <c r="K18" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="L18" s="96"/>
-      <c r="M18" s="97" t="s">
+      <c r="L18" s="93"/>
+      <c r="M18" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="N18" s="97" t="s">
+      <c r="N18" s="94" t="s">
         <v>84</v>
       </c>
-      <c r="O18" s="97"/>
-      <c r="P18" s="97"/>
-      <c r="Q18" s="97"/>
-      <c r="R18" s="97"/>
-      <c r="S18" s="97"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
     </row>
     <row r="19" ht="14.25" spans="1:19">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="36" t="s">
+      <c r="B19" s="46"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="H19" s="61" t="s">
+      <c r="H19" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="I19" s="62"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="99"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="101"/>
-      <c r="N19" s="101"/>
-      <c r="O19" s="101"/>
-      <c r="P19" s="101"/>
-      <c r="Q19" s="101"/>
-      <c r="R19" s="101"/>
-      <c r="S19" s="117"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="99"/>
+      <c r="S19" s="100"/>
     </row>
     <row r="20" ht="14.25" spans="1:19">
-      <c r="A20" s="30"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="31" t="s">
+      <c r="A20" s="48"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="31"/>
-      <c r="G20" s="62" t="s">
+      <c r="F20" s="49"/>
+      <c r="G20" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="98" t="s">
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="96" t="s">
         <v>89</v>
       </c>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62" t="s">
+      <c r="K20" s="40"/>
+      <c r="L20" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62" t="s">
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62" t="s">
+      <c r="P20" s="40"/>
+      <c r="Q20" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="R20" s="62"/>
-      <c r="S20" s="61" t="s">
+      <c r="R20" s="40"/>
+      <c r="S20" s="41" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:19">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="47" t="s">
+      <c r="B21" s="70"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="103" t="s">
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="101" t="s">
         <v>95</v>
       </c>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="102"/>
+      <c r="P21" s="74"/>
+      <c r="Q21" s="74"/>
+      <c r="R21" s="74"/>
+      <c r="S21" s="76"/>
     </row>
     <row r="22" ht="14.25" spans="1:19">
-      <c r="A22" s="63"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="67"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="106"/>
-      <c r="R22" s="106"/>
-      <c r="S22" s="113"/>
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="106"/>
+      <c r="O22" s="108"/>
+      <c r="P22" s="109"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="109"/>
+      <c r="S22" s="53"/>
     </row>
     <row r="23" ht="14.25" spans="1:19">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="110" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="69"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72" t="s">
+      <c r="B23" s="111"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="114" t="s">
         <v>97</v>
       </c>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="108"/>
-      <c r="P23" s="109"/>
-      <c r="Q23" s="109"/>
-      <c r="R23" s="109"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="114"/>
+      <c r="O23" s="116"/>
+      <c r="P23" s="117"/>
+      <c r="Q23" s="117"/>
+      <c r="R23" s="117"/>
       <c r="S23" s="118"/>
     </row>
   </sheetData>
@@ -2872,301 +2687,4 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" t="s" s="1">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="B2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="F2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="B4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="B6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="F6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="B8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="B10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="F17" t="s" s="2">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D18" t="s">
-        <v>137</v>
-      </c>
-      <c r="E18" t="s">
-        <v>138</v>
-      </c>
-      <c r="F18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="F20" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C22" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="B24" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="B26" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="B28" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="B30" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>160</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="B4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B8:F9"/>
-    <mergeCell ref="B10:F11"/>
-    <mergeCell ref="B12:F13"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:F29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:F31"/>
-    <mergeCell ref="A33:C35"/>
-    <mergeCell ref="D33:F35"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/declareExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/declareExport.xlsx
@@ -1,15 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="报关单" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -355,8 +353,8 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="180" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
     <numFmt numFmtId="181" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
@@ -841,7 +839,53 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -869,9 +913,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -888,50 +930,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1198,6 +1196,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1213,6 +1214,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1231,62 +1241,122 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1294,7 +1364,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1309,22 +1382,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1336,13 +1427,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1360,19 +1451,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1387,7 +1502,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1402,142 +1526,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1925,7 +1923,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
-      <c r="J1" s="73"/>
+      <c r="J1" s="5"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1937,667 +1935,667 @@
       <c r="S1" s="4"/>
     </row>
     <row r="2" ht="14.25" spans="1:19">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="76" t="s">
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="S2" s="76"/>
+      <c r="S2" s="13"/>
     </row>
     <row r="3" ht="14.25" spans="1:19">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="18"/>
+      <c r="G3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15" t="s">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15" t="s">
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
     </row>
     <row r="4" ht="14.25" spans="1:19">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="19" t="s">
+      <c r="F4" s="21"/>
+      <c r="G4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19" t="s">
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
     </row>
     <row r="5" ht="14.25" spans="1:19">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="13" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="13" t="s">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="78"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
     </row>
     <row r="6" ht="14.25" spans="1:19">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="16" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="79" t="s">
+      <c r="F6" s="21"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="80"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
     </row>
     <row r="7" ht="14.25" spans="1:19">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13" t="s">
+      <c r="B7" s="37"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15" t="s">
+      <c r="F7" s="18"/>
+      <c r="G7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="13" t="s">
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N7" s="78"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="61"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="41"/>
     </row>
     <row r="8" ht="14.25" spans="1:19">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="19" t="s">
+      <c r="F8" s="21"/>
+      <c r="G8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="84" t="s">
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="N8" s="85"/>
-      <c r="O8" s="86"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="45"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
     </row>
     <row r="9" ht="14.25" spans="1:19">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="10" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="30" t="s">
+      <c r="F9" s="14"/>
+      <c r="G9" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="13" t="s">
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="14"/>
-      <c r="M9" s="13" t="s">
+      <c r="L9" s="18"/>
+      <c r="M9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="78"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="112"/>
-      <c r="S9" s="113"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="53"/>
     </row>
     <row r="10" ht="14.25" spans="1:19">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="19" t="s">
+      <c r="F10" s="21"/>
+      <c r="G10" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="16" t="s">
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="19" t="s">
+      <c r="L10" s="21"/>
+      <c r="M10" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="114"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
     </row>
     <row r="11" ht="14.25" spans="1:19">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="13" t="s">
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="14"/>
-      <c r="M11" s="88" t="s">
+      <c r="L11" s="18"/>
+      <c r="M11" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="N11" s="88"/>
-      <c r="O11" s="88" t="s">
+      <c r="N11" s="56"/>
+      <c r="O11" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88" t="s">
+      <c r="P11" s="56"/>
+      <c r="Q11" s="56"/>
+      <c r="R11" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="S11" s="88"/>
+      <c r="S11" s="56"/>
     </row>
     <row r="12" ht="14.25" spans="1:19">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="19" t="s">
+      <c r="B12" s="22"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="F12" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="79" t="s">
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="81"/>
-      <c r="M12" s="89" t="s">
+      <c r="L12" s="35"/>
+      <c r="M12" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19" t="s">
+      <c r="N12" s="24"/>
+      <c r="O12" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19" t="s">
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="S12" s="19"/>
+      <c r="S12" s="24"/>
     </row>
     <row r="13" ht="14.25" spans="1:19">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="90"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="60"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
     </row>
     <row r="14" ht="14.25" spans="1:19">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="115"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="68"/>
     </row>
     <row r="15" ht="14.25" spans="1:19">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="46" t="s">
+      <c r="B15" s="70"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="102"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="76"/>
     </row>
     <row r="16" ht="14.25" spans="1:19">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="91"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="93"/>
-      <c r="P16" s="93"/>
-      <c r="Q16" s="93"/>
-      <c r="R16" s="93"/>
-      <c r="S16" s="116"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="66"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="77"/>
+      <c r="S16" s="78"/>
     </row>
     <row r="17" ht="42.75" spans="1:19">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="48" t="s">
+      <c r="E17" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="G17" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="H17" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="I17" s="48" t="s">
+      <c r="I17" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="J17" s="48" t="s">
+      <c r="J17" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="48" t="s">
+      <c r="K17" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48" t="s">
+      <c r="L17" s="79"/>
+      <c r="M17" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="N17" s="48" t="s">
+      <c r="N17" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="O17" s="48"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="48"/>
-      <c r="S17" s="48"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="79"/>
+      <c r="Q17" s="79"/>
+      <c r="R17" s="79"/>
+      <c r="S17" s="79"/>
     </row>
     <row r="18" ht="28.5" spans="1:19">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="57" t="s">
+      <c r="F18" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="G18" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="H18" s="59" t="s">
+      <c r="H18" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="I18" s="94" t="s">
+      <c r="I18" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="J18" s="94" t="s">
+      <c r="J18" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="K18" s="95" t="s">
+      <c r="K18" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="L18" s="96"/>
-      <c r="M18" s="97" t="s">
+      <c r="L18" s="93"/>
+      <c r="M18" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="N18" s="97" t="s">
+      <c r="N18" s="94" t="s">
         <v>84</v>
       </c>
-      <c r="O18" s="97"/>
-      <c r="P18" s="97"/>
-      <c r="Q18" s="97"/>
-      <c r="R18" s="97"/>
-      <c r="S18" s="97"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
     </row>
     <row r="19" ht="14.25" spans="1:19">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="36" t="s">
+      <c r="B19" s="46"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="H19" s="61" t="s">
+      <c r="H19" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="I19" s="62"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="99"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="101"/>
-      <c r="N19" s="101"/>
-      <c r="O19" s="101"/>
-      <c r="P19" s="101"/>
-      <c r="Q19" s="101"/>
-      <c r="R19" s="101"/>
-      <c r="S19" s="117"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="99"/>
+      <c r="S19" s="100"/>
     </row>
     <row r="20" ht="14.25" spans="1:19">
-      <c r="A20" s="30"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="31" t="s">
+      <c r="A20" s="48"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="31"/>
-      <c r="G20" s="62" t="s">
+      <c r="F20" s="49"/>
+      <c r="G20" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="98" t="s">
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="96" t="s">
         <v>89</v>
       </c>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62" t="s">
+      <c r="K20" s="40"/>
+      <c r="L20" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62" t="s">
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62" t="s">
+      <c r="P20" s="40"/>
+      <c r="Q20" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="R20" s="62"/>
-      <c r="S20" s="61" t="s">
+      <c r="R20" s="40"/>
+      <c r="S20" s="41" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:19">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="47" t="s">
+      <c r="B21" s="70"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="103" t="s">
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="101" t="s">
         <v>95</v>
       </c>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="102"/>
+      <c r="P21" s="74"/>
+      <c r="Q21" s="74"/>
+      <c r="R21" s="74"/>
+      <c r="S21" s="76"/>
     </row>
     <row r="22" ht="14.25" spans="1:19">
-      <c r="A22" s="63"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="67"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="106"/>
-      <c r="R22" s="106"/>
-      <c r="S22" s="113"/>
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="106"/>
+      <c r="O22" s="108"/>
+      <c r="P22" s="109"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="109"/>
+      <c r="S22" s="53"/>
     </row>
     <row r="23" ht="14.25" spans="1:19">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="110" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="69"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72" t="s">
+      <c r="B23" s="111"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="114" t="s">
         <v>97</v>
       </c>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="108"/>
-      <c r="P23" s="109"/>
-      <c r="Q23" s="109"/>
-      <c r="R23" s="109"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="114"/>
+      <c r="O23" s="116"/>
+      <c r="P23" s="117"/>
+      <c r="Q23" s="117"/>
+      <c r="R23" s="117"/>
       <c r="S23" s="118"/>
     </row>
   </sheetData>
@@ -2689,28 +2687,4 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>